--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC VIII/LTAIPT_A63F08B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC VIII/LTAIPT_A63F08B.xlsx
@@ -100,28 +100,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>13CEC5F52FD7914298999BC98983D6BE</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t/>
+    <t>94DDDB9BA51F40BC601E7B389801AD53</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto%20Recursos%20Humanos/1er%20Trimestre/Tabulador%202023.%20Of.D.AD.0357-2023.pdf</t>
   </si>
   <si>
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>17/01/2023</t>
-  </si>
-  <si>
-    <t>El tabulador de sueldos 2022 se encuentra en proceso de aurización, mediante Oficio D.AD.300/2022 en Oficialia Mayor de Gobierno.</t>
+    <t>19/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo del 2023, El tabulador de sueldos 2023 de este Colegio de Bachilleres del Estado de Tlaxcala,se encuentra en proceso de autorización, mediante OFICIO DIR.AD.0357/2023 ante Oficialia Mayor de Gobierno.</t>
   </si>
 </sst>
 </file>
@@ -517,15 +517,15 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="137.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="144.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="112.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="223.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
